--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2BD1FB8-79E6-4C13-BD4E-3548AA799969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CA9CD6-57CF-46EC-98A1-E604E71850C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
+    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDataTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>SkillID</t>
   </si>
@@ -28,19 +28,46 @@
     <t>SkillName</t>
   </si>
   <si>
-    <t>SrvIndex</t>
-  </si>
-  <si>
     <t>Cooldown</t>
   </si>
   <si>
-    <t>MansCost</t>
-  </si>
-  <si>
     <t>Rasengan</t>
   </si>
   <si>
+    <t>Fireball</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Chidori</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Big_Rasengan</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rasen_Shuriken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimStateName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rasengan</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LoopDurationSec</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsHoldSkill</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_RasenShuriken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -992,10 +1019,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7395922-27B8-4533-BFE6-6C196B1AE7C3}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="43.375" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="27.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1006,44 +1041,104 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
         <v>8</v>
       </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
       <c r="E2">
-        <v>30</v>
+        <v>3</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CA9CD6-57CF-46EC-98A1-E604E71850C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A91F81-A060-432C-BF7E-7CE0041E23CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDataTable" sheetId="1" r:id="rId1"/>
@@ -1064,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A91F81-A060-432C-BF7E-7CE0041E23CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD40C223-952D-4D57-947D-23E7DE68AB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
@@ -1084,10 +1084,10 @@
         <v>12</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD40C223-952D-4D57-947D-23E7DE68AB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F5E47C-6871-4072-8D07-AC2AB56C29CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F5E47C-6871-4072-8D07-AC2AB56C29CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080176A6-0F61-4043-82CA-946B8A6E3F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>SkillID</t>
   </si>
@@ -34,10 +34,6 @@
     <t>Rasengan</t>
   </si>
   <si>
-    <t>Fireball</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Chidori</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -67,6 +63,56 @@
   </si>
   <si>
     <t>Skill_RasenShuriken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BlastboomDance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Chidori</t>
+  </si>
+  <si>
+    <t>Skill_BlastBoomDance</t>
+  </si>
+  <si>
+    <t>hasDashPhase</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dashSpeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxDashDistance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>targetStopDistance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>attackEndAnimStateName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rasengan_End</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>airAnimStateName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>airGravityOff</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rasengan_Air</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_RasenShuriken_Air</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1019,18 +1065,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7395922-27B8-4533-BFE6-6C196B1AE7C3}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="43.375" customWidth="1"/>
-    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="27.625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="13" max="13" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1041,16 +1094,37 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
-        <v>11</v>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1061,27 +1135,48 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1089,8 +1184,26 @@
       <c r="F3" t="b">
         <v>0</v>
       </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>20</v>
+      </c>
+      <c r="J3">
+        <v>1.5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1100,36 +1213,72 @@
       <c r="C4">
         <v>5</v>
       </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
       <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="b">
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1139,6 +1288,21 @@
       </c>
       <c r="F6" t="b">
         <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>1.5</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080176A6-0F61-4043-82CA-946B8A6E3F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD541A5A-FD66-4C06-A61B-A8F35B0EEABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD541A5A-FD66-4C06-A61B-A8F35B0EEABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05878BFA-3658-4E4D-95D7-98B1C55DB02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>SkillID</t>
   </si>
@@ -113,6 +113,14 @@
   </si>
   <si>
     <t>Skill_RasenShuriken_Air</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Chidori_End</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Chidori_Air</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1234,8 +1242,14 @@
       <c r="J4">
         <v>1.5</v>
       </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
       <c r="M4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05878BFA-3658-4E4D-95D7-98B1C55DB02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CABC80-E161-46E9-B884-8CA16AEA7D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDataTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>SkillID</t>
   </si>
@@ -66,16 +66,9 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>BlastboomDance</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_Chidori</t>
   </si>
   <si>
-    <t>Skill_BlastBoomDance</t>
-  </si>
-  <si>
     <t>hasDashPhase</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -121,6 +114,18 @@
   </si>
   <si>
     <t>Skill_Chidori_Air</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireBall</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_FireBall</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_FireBall_Air</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1111,25 +1116,25 @@
         <v>10</v>
       </c>
       <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" t="s">
-        <v>21</v>
-      </c>
       <c r="M1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1158,19 +1163,19 @@
         <v>14</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J2">
         <v>1.5</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1205,7 +1210,7 @@
         <v>1.5</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -1216,22 +1221,22 @@
         <v>1003</v>
       </c>
       <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1242,11 +1247,8 @@
       <c r="J4">
         <v>1.5</v>
       </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -1257,31 +1259,37 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>14</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J5">
         <v>1.5</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CABC80-E161-46E9-B884-8CA16AEA7D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA6591C-929D-46FD-B6F2-0B0BBFF65B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDataTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>SkillID</t>
   </si>
@@ -126,6 +126,29 @@
   </si>
   <si>
     <t>Skill_FireBall_Air</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>airLandedAnimStateName</t>
+  </si>
+  <si>
+    <t>Skill_Rasengan_Landed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Chidori_Landed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>airAttackEndAnimStateName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rasengan_Air_End</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Chidori_Air_End</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1078,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7395922-27B8-4533-BFE6-6C196B1AE7C3}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
@@ -1094,9 +1117,11 @@
     <col min="11" max="11" width="25.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.5" customWidth="1"/>
     <col min="13" max="13" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1136,8 +1161,14 @@
       <c r="M1" t="s">
         <v>20</v>
       </c>
+      <c r="N1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1145,13 +1176,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1177,8 +1208,14 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -1186,7 +1223,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1216,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1254,7 +1291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1268,7 +1305,7 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1294,8 +1331,14 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA6591C-929D-46FD-B6F2-0B0BBFF65B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C8A67B-A691-415D-A9ED-1AC47C9DC846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDataTable" sheetId="1" r:id="rId1"/>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C8A67B-A691-415D-A9ED-1AC47C9DC846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E13383-5215-499C-AE2E-72A650F40230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDataTable" sheetId="1" r:id="rId1"/>
@@ -1261,7 +1261,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -1299,7 +1299,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -1320,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="J5">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="s">
         <v>23</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E13383-5215-499C-AE2E-72A650F40230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0225C5-FC97-435A-BAF2-CAC41AE40B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDataTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>SkillID</t>
   </si>
@@ -149,6 +149,10 @@
   </si>
   <si>
     <t>Skill_Chidori_Air_End</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignoreTargetStop</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1101,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7395922-27B8-4533-BFE6-6C196B1AE7C3}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
@@ -1114,14 +1118,15 @@
     <col min="8" max="8" width="10.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.5" customWidth="1"/>
-    <col min="13" max="13" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5" customWidth="1"/>
+    <col min="14" max="14" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1153,22 +1158,25 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>28</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1199,23 +1207,26 @@
       <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="b">
+      <c r="N2" t="b">
         <v>1</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -1246,14 +1257,17 @@
       <c r="J3">
         <v>1.5</v>
       </c>
-      <c r="L3" t="s">
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="b">
+      <c r="N3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1284,14 +1298,17 @@
       <c r="J4">
         <v>1.5</v>
       </c>
-      <c r="L4" t="s">
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
         <v>27</v>
       </c>
-      <c r="M4" t="b">
+      <c r="N4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1314,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I5">
         <v>12</v>
@@ -1322,23 +1339,26 @@
       <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
         <v>23</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>24</v>
       </c>
-      <c r="M5" t="b">
+      <c r="N5" t="b">
         <v>1</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>30</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -1348,25 +1368,7 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>1.5</v>
-      </c>
-      <c r="M6" t="b">
+      <c r="N6" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0225C5-FC97-435A-BAF2-CAC41AE40B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33DD018-2CEE-440E-ACA9-2A2D47B2CA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>SkillID</t>
   </si>
@@ -38,10 +38,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Big_Rasengan</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Rasen_Shuriken</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -153,6 +149,34 @@
   </si>
   <si>
     <t>ignoreTargetStop</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>uiSlotIndex</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>uiIconSrvIndex</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sub</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Replacement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shuriken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillCategory</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1105,7 +1129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7395922-27B8-4533-BFE6-6C196B1AE7C3}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
@@ -1124,9 +1148,12 @@
     <col min="14" max="14" width="12.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="25.125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1137,46 +1164,55 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
       <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" t="s">
         <v>34</v>
       </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" t="s">
-        <v>31</v>
+      <c r="S1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1187,7 +1223,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>15</v>
@@ -1211,33 +1247,42 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2">
+        <v>-1</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1261,24 +1306,33 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3">
+        <v>-1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1302,13 +1356,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4">
+        <v>-1</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1319,7 +1382,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>15</v>
@@ -1343,33 +1406,122 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
         <v>23</v>
-      </c>
-      <c r="M5" t="s">
-        <v>24</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P5" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5">
+        <v>-1</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1005</v>
+        <v>2001</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
       <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2002</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33DD018-2CEE-440E-ACA9-2A2D47B2CA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696004B2-21DC-4B80-B2E3-7E3959AAD5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>SkillID</t>
   </si>
@@ -177,6 +177,23 @@
   </si>
   <si>
     <t>skillCategory</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShinsuSenju</t>
+  </si>
+  <si>
+    <t>Kirin</t>
+  </si>
+  <si>
+    <t>Skill_ShinsuSenju</t>
+  </si>
+  <si>
+    <t>Skill_Kirin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ultimate</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1129,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7395922-27B8-4533-BFE6-6C196B1AE7C3}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
@@ -1524,6 +1541,94 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>45</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>45</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696004B2-21DC-4B80-B2E3-7E3959AAD5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC244B0-5A6A-4435-B0C0-DE540797823C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
@@ -183,17 +183,18 @@
     <t>ShinsuSenju</t>
   </si>
   <si>
-    <t>Kirin</t>
-  </si>
-  <si>
     <t>Skill_ShinsuSenju</t>
   </si>
   <si>
-    <t>Skill_Kirin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Ultimate</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kamui</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Kamui</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1552,7 +1553,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1576,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1590,13 +1591,13 @@
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1620,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="R9">
         <v>1</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_SkilLData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC244B0-5A6A-4435-B0C0-DE540797823C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC526D5B-B020-40CF-9BBF-01AA477DFA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FF045EB-CA47-4F87-A666-41B179691649}"/>
   </bookViews>
@@ -1315,7 +1315,7 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>1.5</v>
@@ -1365,7 +1365,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>1.5</v>
